--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.88.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.88.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.88" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.88" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.88.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.88.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0088.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0088.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -847,7 +847,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.88.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.88.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.88" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.88" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,8 +431,8 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
@@ -605,19 +605,23 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L1: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: 80.â€�</t>
+          <t>L11: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L1: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: ï»¿o.â€�</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]o.”</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]o.”</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L40: isolated marker/symbol line :: 81</t>
+          <t>L1: symbol-only separator/garbage line :: 80.”</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -668,19 +672,19 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L38: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: 80.â€�</t>
+          <t>L63: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: PROCEEDINGS TO HEAR CAUSE Â« PRO CONFESSO.â€�</t>
+          <t>L103: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L43: symbol-only separator/garbage line :: 1845.</t>
+          <t>L11: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
@@ -722,16 +726,12 @@
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr"/>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L103: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L47: symbol-only separator/garbage line :: 77.</t>
+          <t>L38: symbol-only separator/garbage line :: 80.”</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -758,12 +758,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -778,7 +778,7 @@
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L60: symbol-only separator/garbage line :: 78.</t>
+          <t>L40: isolated marker/symbol line :: 81</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -825,7 +825,7 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L96: symbol-only separator/garbage line :: 79.</t>
+          <t>L43: symbol-only separator/garbage line :: 1845.</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
@@ -872,7 +872,7 @@
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L107: isolated marker/symbol line :: 4</t>
+          <t>L47: symbol-only separator/garbage line :: 77.</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
@@ -919,12 +919,12 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L121: isolated marker/symbol line :: F</t>
+          <t>L60: symbol-only separator/garbage line :: 78.</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L103: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L103: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -964,7 +964,11 @@
       <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
-      <c r="N9" s="1" t="inlineStr"/>
+      <c r="N9" s="1" t="inlineStr">
+        <is>
+          <t>L63: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
       <c r="O9" s="1" t="inlineStr"/>
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr"/>
@@ -990,7 +994,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1003,7 +1007,11 @@
       <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
-      <c r="N10" s="1" t="inlineStr"/>
+      <c r="N10" s="1" t="inlineStr">
+        <is>
+          <t>L96: symbol-only separator/garbage line :: 79.</t>
+        </is>
+      </c>
       <c r="O10" s="1" t="inlineStr"/>
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
@@ -1029,7 +1037,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1042,7 +1050,11 @@
       <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
-      <c r="N11" s="1" t="inlineStr"/>
+      <c r="N11" s="1" t="inlineStr">
+        <is>
+          <t>L107: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
       <c r="O11" s="1" t="inlineStr"/>
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr"/>
@@ -1063,7 +1075,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1081,7 +1093,11 @@
       <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
-      <c r="N12" s="1" t="inlineStr"/>
+      <c r="N12" s="1" t="inlineStr">
+        <is>
+          <t>L121: isolated marker/symbol line :: F</t>
+        </is>
+      </c>
       <c r="O12" s="1" t="inlineStr"/>
       <c r="P12" s="1" t="inlineStr"/>
       <c r="Q12" s="1" t="inlineStr"/>
